--- a/docs/result/row-data/2nd-test/pessimistic/pessimistic-lock-500-ngrinder-result.xlsx
+++ b/docs/result/row-data/2nd-test/pessimistic/pessimistic-lock-500-ngrinder-result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sangja/Projects/concurrency-control-benchmarks/docs/result/row-data/2nd-test/pessimistic/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C8595A-EE38-8240-A893-9438BB6A31EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E0411D-7F70-B946-B415-C93B8FCF0457}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14700" yWindow="660" windowWidth="14700" windowHeight="18460" xr2:uid="{E6939166-50FA-584A-8F99-D0D195A321FF}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="14700" windowHeight="18460" xr2:uid="{E6939166-50FA-584A-8F99-D0D195A321FF}"/>
   </bookViews>
   <sheets>
     <sheet name="pessimistic-lock-500-ngrinder-r" sheetId="1" r:id="rId1"/>
@@ -4789,6 +4789,1464 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="738151" cy="355097"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="20" name="TextBox 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EE302A3-D510-8A42-A25F-8ACE31576C84}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4838700" y="3657600"/>
+              <a:ext cx="738151" cy="355097"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:d>
+                      <m:dPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑛</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑖</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−1</m:t>
+                        </m:r>
+                      </m:e>
+                    </m:d>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+            <a:p>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="20" name="TextBox 19">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0EE302A3-D510-8A42-A25F-8ACE31576C84}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4838700" y="3657600"/>
+              <a:ext cx="738151" cy="355097"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>(𝑛_𝑖−1) </a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝜎_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑖^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+            <a:p>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1599284" cy="182871"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="21" name="TextBox 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B15C037A-4241-224A-B7A6-17CF2DD2373F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4838700" y="4800600"/>
+              <a:ext cx="1599284" cy="182871"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑆</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑆</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑤𝑖𝑡h𝑖𝑛</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:sty m:val="p"/>
+                          </m:rPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>Σ</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>=1</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                    <m:d>
+                      <m:dPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:dPr>
+                      <m:e>
+                        <m:sSub>
+                          <m:sSubPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSubPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑛</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑖</m:t>
+                            </m:r>
+                          </m:sub>
+                        </m:sSub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>−1</m:t>
+                        </m:r>
+                      </m:e>
+                    </m:d>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="21" name="TextBox 20">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B15C037A-4241-224A-B7A6-17CF2DD2373F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4838700" y="4800600"/>
+              <a:ext cx="1599284" cy="182871"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑆𝑆_𝑤𝑖𝑡ℎ𝑖𝑛=Σ_(𝑖=1)^2 (𝑛_𝑖−1) 𝜎_𝑖^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="964816" cy="177228"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="22" name="TextBox 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E07A0267-8730-274E-8A41-087C09036AE5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4838700" y="5257800"/>
+              <a:ext cx="964816" cy="177228"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑛</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:d>
+                          <m:dPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:dPr>
+                          <m:e>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑖</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡𝑜𝑡𝑎𝑙</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                        </m:d>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="22" name="TextBox 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E07A0267-8730-274E-8A41-087C09036AE5}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4838700" y="5257800"/>
+              <a:ext cx="964816" cy="177228"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑛_𝑖 (𝜇_𝑖−𝜇_𝑡𝑜𝑡𝑎𝑙 )^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1984902" cy="186782"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="23" name="TextBox 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{465056EC-7734-4247-A7FA-78550161DB5F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4838700" y="6400800"/>
+              <a:ext cx="1984902" cy="186782"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>𝑆</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑆</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑏𝑒𝑡𝑤𝑒𝑒𝑛</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:sSubSup>
+                      <m:sSubSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubSupPr>
+                      <m:e>
+                        <m:r>
+                          <m:rPr>
+                            <m:sty m:val="p"/>
+                          </m:rPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>Σ</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>=1</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑘</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSubSup>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑛</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑖</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:d>
+                          <m:dPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:dPr>
+                          <m:e>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑖</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝜇</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑡𝑜𝑡𝑎𝑙</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:e>
+                        </m:d>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>2</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="23" name="TextBox 22">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{465056EC-7734-4247-A7FA-78550161DB5F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4838700" y="6400800"/>
+              <a:ext cx="1984902" cy="186782"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝑆𝑆_𝑏𝑒𝑡𝑤𝑒𝑒𝑛=Σ_(𝑖=1)^𝑘 𝑛_𝑖 (𝜇_𝑖−𝜇_𝑡𝑜𝑡𝑎𝑙 )^2</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1842235" cy="500137"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="24" name="TextBox 23">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22030784-8822-A543-A1ED-58120B749DC1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4838700" y="6858000"/>
+              <a:ext cx="1842235" cy="500137"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                            <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <m:rPr>
+                            <m:sty m:val="p"/>
+                          </m:rPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>total</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:rad>
+                      <m:radPr>
+                        <m:degHide m:val="on"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:radPr>
+                      <m:deg/>
+                      <m:e>
+                        <m:f>
+                          <m:fPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:fPr>
+                          <m:num>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>SS</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>within</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>+</m:t>
+                            </m:r>
+                            <m:sSub>
+                              <m:sSubPr>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:sSubPr>
+                              <m:e>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>SS</m:t>
+                                </m:r>
+                              </m:e>
+                              <m:sub>
+                                <m:r>
+                                  <m:rPr>
+                                    <m:sty m:val="p"/>
+                                  </m:rPr>
+                                  <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                    <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>between</m:t>
+                                </m:r>
+                              </m:sub>
+                            </m:sSub>
+                          </m:num>
+                          <m:den>
+                            <m:r>
+                              <m:rPr>
+                                <m:sty m:val="p"/>
+                              </m:rPr>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>N</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                                <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                              </a:rPr>
+                              <m:t>-1</m:t>
+                            </m:r>
+                          </m:den>
+                        </m:f>
+                      </m:e>
+                    </m:rad>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="24" name="TextBox 23">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22030784-8822-A543-A1ED-58120B749DC1}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4838700" y="6858000"/>
+              <a:ext cx="1842235" cy="500137"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>𝜎_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>total=√((SS_within+SS_between)/(N-1))</a:t>
+              </a:r>
+              <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="438710" cy="173766"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="25" name="TextBox 24">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1D201B5-C62C-9842-B1BB-CD085CE43C0B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4838700" y="7543800"/>
+              <a:ext cx="438710" cy="173766"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                        <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                      </a:rPr>
+                      <m:t>2</m:t>
+                    </m:r>
+                    <m:sSub>
+                      <m:sSubPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSubPr>
+                      <m:e>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝜎</m:t>
+                        </m:r>
+                      </m:e>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="1">
+                            <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑡𝑜𝑡𝑎𝑙</m:t>
+                        </m:r>
+                      </m:sub>
+                    </m:sSub>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="25" name="TextBox 24">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1D201B5-C62C-9842-B1BB-CD085CE43C0B}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="4838700" y="7543800"/>
+              <a:ext cx="438710" cy="173766"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" lIns="0" tIns="0" rIns="0" bIns="0" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="0" i="0">
+                  <a:latin typeface="Cambria Math" panose="02040503050406030204" pitchFamily="18" charset="0"/>
+                </a:rPr>
+                <a:t>2𝜎_𝑡𝑜𝑡𝑎𝑙</a:t>
+              </a:r>
+              <a:endParaRPr lang="en-US" altLang="ko-KR" sz="1100" b="0"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -5115,7 +6573,7 @@
     <col min="1" max="1" width="30.28515625" customWidth="1"/>
     <col min="2" max="2" width="14.7109375" customWidth="1"/>
     <col min="3" max="3" width="9.42578125" customWidth="1"/>
-    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" customWidth="1"/>
     <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.7109375" bestFit="1" customWidth="1"/>
@@ -5443,187 +6901,253 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17" spans="2:5">
       <c r="B17">
         <f>A11*B11</f>
         <v>9574.0049999999992</v>
       </c>
+      <c r="E17">
+        <f>(A11-1)*POWER(C11,2)</f>
+        <v>606981.26020599995</v>
+      </c>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18" spans="2:5">
       <c r="B18">
         <f>A12*B12</f>
         <v>158385.04500000001</v>
       </c>
+      <c r="E18">
+        <f>(A12-1)*POWER(C12,2)</f>
+        <v>23217190.570084002</v>
+      </c>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19" spans="2:5">
       <c r="B19">
         <f>A13*B13</f>
         <v>56369.016000000003</v>
       </c>
+      <c r="E19">
+        <f>(A13-1)*POWER(C13,2)</f>
+        <v>9815776.2782279998</v>
+      </c>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20" spans="2:5">
       <c r="B20">
         <f>A14*B14</f>
         <v>90</v>
       </c>
+      <c r="E20">
+        <f>(A14-1)*POWER(C14,2)</f>
+        <v>55.125</v>
+      </c>
     </row>
-    <row r="21" spans="2:2">
+    <row r="21" spans="2:5">
       <c r="B21">
         <f>A15*B15</f>
         <v>9</v>
       </c>
+      <c r="E21">
+        <f>(A15-1)*POWER(C15,2)</f>
+        <v>0</v>
+      </c>
     </row>
-    <row r="22" spans="2:2">
+    <row r="22" spans="2:5">
       <c r="B22">
         <f>SUM(B17:B21)</f>
         <v>224427.06600000002</v>
       </c>
+      <c r="E22">
+        <f>SUM(E17:E21)</f>
+        <v>33640003.233518004</v>
+      </c>
     </row>
-    <row r="23" spans="2:2">
+    <row r="23" spans="2:5">
       <c r="B23">
         <f>SUM(A11:A15)</f>
         <v>500</v>
       </c>
     </row>
-    <row r="24" spans="2:2">
+    <row r="24" spans="2:5">
       <c r="B24">
         <f>B22/B23</f>
         <v>448.85413200000005</v>
       </c>
+      <c r="E24">
+        <f>A11*POWER(B11-B$24,2)</f>
+        <v>11509848.264097659</v>
+      </c>
     </row>
-    <row r="25" spans="2:2">
+    <row r="25" spans="2:5">
       <c r="B25">
         <f>ROUND(B24,2)</f>
         <v>448.85</v>
       </c>
+      <c r="E25">
+        <f>A12*POWER(B12-B$24,2)</f>
+        <v>24845232.88106738</v>
+      </c>
     </row>
-    <row r="27" spans="2:2">
+    <row r="26" spans="2:5">
+      <c r="E26">
+        <f>A13*POWER(B13-B$24,2)</f>
+        <v>5335942.7053915169</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
       <c r="B27">
         <f>POWER(C11,2)</f>
         <v>6457.2474489999995</v>
       </c>
+      <c r="E27">
+        <f>A14*POWER(B14-B$24,2)</f>
+        <v>1733336.5425612612</v>
+      </c>
     </row>
-    <row r="28" spans="2:2">
+    <row r="28" spans="2:5">
       <c r="B28">
         <f>POWER(C12,2)</f>
         <v>118455.053929</v>
       </c>
+      <c r="E28">
+        <f>A15*POWER(B15-B$24,2)</f>
+        <v>193471.65743747348</v>
+      </c>
     </row>
-    <row r="29" spans="2:2">
+    <row r="29" spans="2:5">
       <c r="B29">
         <f>POWER(C13,2)</f>
         <v>49826.275523999997</v>
       </c>
+      <c r="E29">
+        <f>SUM(E24:E28)</f>
+        <v>43617832.050555296</v>
+      </c>
     </row>
-    <row r="30" spans="2:2">
+    <row r="30" spans="2:5">
       <c r="B30">
         <f>POWER(C14,2)</f>
         <v>6.890625</v>
       </c>
     </row>
-    <row r="31" spans="2:2">
+    <row r="31" spans="2:5">
       <c r="B31">
         <f>POWER(C15,2)</f>
         <v>0</v>
       </c>
+      <c r="E31">
+        <f>SQRT((E22+E29)/(B23-1))</f>
+        <v>393.47848887908435</v>
+      </c>
     </row>
-    <row r="32" spans="2:2">
+    <row r="32" spans="2:5">
       <c r="B32">
         <f>POWER(B11,2)</f>
         <v>10156.406841</v>
       </c>
+      <c r="E32">
+        <f>ROUND(E31,2)</f>
+        <v>393.48</v>
+      </c>
     </row>
-    <row r="33" spans="2:2">
+    <row r="33" spans="2:5">
       <c r="B33">
         <f>POWER(B12,2)</f>
         <v>646391.88022499997</v>
       </c>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:5">
       <c r="B34">
         <f>POWER(B13,2)</f>
         <v>81049.534864000001</v>
       </c>
+      <c r="E34">
+        <f>2*E31</f>
+        <v>786.9569777581687</v>
+      </c>
     </row>
-    <row r="35" spans="2:2">
+    <row r="35" spans="2:5">
       <c r="B35">
         <f>POWER(B14,2)</f>
         <v>100</v>
       </c>
+      <c r="E35">
+        <f>ROUND(E34,2)</f>
+        <v>786.96</v>
+      </c>
     </row>
-    <row r="36" spans="2:2">
+    <row r="36" spans="2:5">
       <c r="B36">
         <f>POWER(B15,2)</f>
         <v>81</v>
       </c>
     </row>
-    <row r="37" spans="2:2">
+    <row r="37" spans="2:5">
       <c r="B37">
         <f>B27+B32</f>
         <v>16613.654289999999</v>
       </c>
     </row>
-    <row r="38" spans="2:2">
+    <row r="38" spans="2:5">
       <c r="B38">
         <f>B28+B33</f>
         <v>764846.93415400002</v>
       </c>
     </row>
-    <row r="39" spans="2:2">
+    <row r="39" spans="2:5">
       <c r="B39">
         <f>B29+B34</f>
         <v>130875.810388</v>
       </c>
     </row>
-    <row r="40" spans="2:2">
+    <row r="40" spans="2:5">
       <c r="B40">
         <f>B30+B35</f>
         <v>106.890625</v>
       </c>
     </row>
-    <row r="41" spans="2:2">
+    <row r="41" spans="2:5">
       <c r="B41">
         <f>B31+B36</f>
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="2:2">
+    <row r="42" spans="2:5">
       <c r="B42">
         <f>A11*B37</f>
         <v>1578297.1575499999</v>
       </c>
     </row>
-    <row r="43" spans="2:2">
+    <row r="43" spans="2:5">
       <c r="B43">
         <f>A12*B38</f>
         <v>150674846.02833802</v>
       </c>
     </row>
-    <row r="44" spans="2:2">
+    <row r="44" spans="2:5">
       <c r="B44">
         <f>A13*B39</f>
         <v>25913410.456824001</v>
       </c>
     </row>
-    <row r="45" spans="2:2">
+    <row r="45" spans="2:5">
       <c r="B45">
         <f>A14*B40</f>
         <v>962.015625</v>
       </c>
     </row>
-    <row r="46" spans="2:2">
+    <row r="46" spans="2:5">
       <c r="B46">
         <f>A15*B41</f>
         <v>81</v>
       </c>
     </row>
-    <row r="47" spans="2:2">
+    <row r="47" spans="2:5">
       <c r="B47">
         <f>SUM(B42:B46)</f>
         <v>178167596.65833703</v>
       </c>
     </row>
-    <row r="48" spans="2:2">
+    <row r="48" spans="2:5">
       <c r="B48">
         <f>B47/B23</f>
         <v>356335.19331667403</v>
